--- a/Timesheet-Project/Timesheet 3/Buhle/Buhle_Mukhuba_May_FinalWeek.xlsx
+++ b/Timesheet-Project/Timesheet 3/Buhle/Buhle_Mukhuba_May_FinalWeek.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30224"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sc_LwazisileMhlambi_2026\Timesheet-Project\Timesheet 3\Buhle\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://northerndata.sharepoint.com/sites/SambeGraduateProgramme2025/Shared Documents/Graduates 2026/Timesheet/May 2026/Buhle Mukhuba's Timesheet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="401" documentId="8_{EB71F199-94A3-4318-8A77-751A556C898F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0939DF9A-E46D-40B8-BC45-3B3EA9EB5C16}"/>
+  <xr:revisionPtr revIDLastSave="407" documentId="8_{EB71F199-94A3-4318-8A77-751A556C898F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7576FEB9-E7DE-4F62-A95F-ED57270EB9C3}"/>
   <bookViews>
-    <workbookView xWindow="1116" yWindow="1116" windowWidth="17280" windowHeight="8880" xr2:uid="{1C8F8026-B005-4B08-94D3-371A77F74D8F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1C8F8026-B005-4B08-94D3-371A77F74D8F}"/>
   </bookViews>
   <sheets>
     <sheet name="May" sheetId="1" r:id="rId1"/>
     <sheet name="Key" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,15 +39,21 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="198">
   <si>
+    <t>Consultant</t>
+  </si>
+  <si>
+    <t>Buhle</t>
+  </si>
+  <si>
+    <t>Total Billable Hours</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
     <t>D of Week</t>
   </si>
   <si>
-    <t>Consultant</t>
-  </si>
-  <si>
     <t>Client</t>
   </si>
   <si>
@@ -75,562 +81,556 @@
     <t>Friday</t>
   </si>
   <si>
+    <t>Internal Sambe</t>
+  </si>
+  <si>
+    <t>Public Holiday</t>
+  </si>
+  <si>
+    <t>Non-Billable</t>
+  </si>
+  <si>
+    <t>Worker's Day</t>
+  </si>
+  <si>
+    <t>Saturday</t>
+  </si>
+  <si>
+    <t>Sunday</t>
+  </si>
+  <si>
+    <t>Monday</t>
+  </si>
+  <si>
+    <t>Meeting</t>
+  </si>
+  <si>
+    <t>Discovery Induction</t>
+  </si>
+  <si>
+    <t>Tuesday</t>
+  </si>
+  <si>
+    <t>Wednesday</t>
+  </si>
+  <si>
+    <t>Thursday</t>
+  </si>
+  <si>
+    <t>Attended high performers standup</t>
+  </si>
+  <si>
+    <t>Research</t>
+  </si>
+  <si>
+    <t>Udemy - Ms SQL Server DBA</t>
+  </si>
+  <si>
+    <t>Attended team meeting</t>
+  </si>
+  <si>
+    <t>Attended midday check-in</t>
+  </si>
+  <si>
+    <t>Attended high performers retrospective meeting</t>
+  </si>
+  <si>
+    <t>Annual Leave</t>
+  </si>
+  <si>
+    <t>Udemy - SSIS Introduction</t>
+  </si>
+  <si>
+    <t>Client Communication</t>
+  </si>
+  <si>
+    <t>Udemy - Ms SQL Server T-SQL</t>
+  </si>
+  <si>
+    <t>Presentation - Dashboard</t>
+  </si>
+  <si>
+    <t>Forcasted Hours</t>
+  </si>
+  <si>
+    <t>Forcasted Work Days this month</t>
+  </si>
+  <si>
+    <t>Line Manager :</t>
+  </si>
+  <si>
+    <t>Billable Hours</t>
+  </si>
+  <si>
+    <t>Contractor:</t>
+  </si>
+  <si>
+    <t>Non Billable Hours</t>
+  </si>
+  <si>
+    <t>Total of All Hours</t>
+  </si>
+  <si>
+    <t>Plus: Hours worked, not claimed</t>
+  </si>
+  <si>
+    <t>Work</t>
+  </si>
+  <si>
+    <t>Resource</t>
+  </si>
+  <si>
+    <t>Billable</t>
+  </si>
+  <si>
+    <t>ADVTech</t>
+  </si>
+  <si>
+    <t>Recording Cvs on Workbook Sheet</t>
+  </si>
+  <si>
+    <t>.NET code</t>
+  </si>
+  <si>
+    <t>Amanda</t>
+  </si>
+  <si>
+    <t>AFA Sasfin</t>
+  </si>
+  <si>
+    <t>Placing Cvs in Templates</t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>Angela</t>
+  </si>
+  <si>
+    <t>Artist Proof Studio</t>
+  </si>
+  <si>
+    <t>Screening</t>
+  </si>
+  <si>
+    <t>Analysis</t>
+  </si>
+  <si>
+    <t>Aubrey</t>
+  </si>
+  <si>
+    <t>Assimil8</t>
+  </si>
+  <si>
+    <t>Headhunting</t>
+  </si>
+  <si>
+    <t>Architecture</t>
+  </si>
+  <si>
+    <t>Avinash</t>
+  </si>
+  <si>
+    <t>Base 3</t>
+  </si>
+  <si>
+    <t>Interviews</t>
+  </si>
+  <si>
+    <t>Training</t>
+  </si>
+  <si>
     <t>Bhavesh</t>
   </si>
   <si>
-    <t>Billable</t>
-  </si>
-  <si>
-    <t>Saturday</t>
-  </si>
-  <si>
-    <t>Non-Billable</t>
-  </si>
-  <si>
-    <t>Sunday</t>
-  </si>
-  <si>
-    <t>Monday</t>
-  </si>
-  <si>
-    <t>Tuesday</t>
-  </si>
-  <si>
-    <t>Wednesday</t>
-  </si>
-  <si>
-    <t>Thursday</t>
-  </si>
-  <si>
-    <t>Forcasted Hours</t>
-  </si>
-  <si>
-    <t>Forcasted Work Days this month</t>
-  </si>
-  <si>
-    <t>Line Manager :</t>
-  </si>
-  <si>
-    <t>Billable Hours</t>
-  </si>
-  <si>
-    <t>Contractor:</t>
-  </si>
-  <si>
-    <t>Non Billable Hours</t>
-  </si>
-  <si>
-    <t>Total of All Hours</t>
-  </si>
-  <si>
-    <t>Plus: Hours worked, not claimed</t>
-  </si>
-  <si>
-    <t>Resource</t>
-  </si>
-  <si>
-    <t>Recording Cvs on Workbook Sheet</t>
-  </si>
-  <si>
-    <t>.NET code</t>
-  </si>
-  <si>
-    <t>Placing Cvs in Templates</t>
-  </si>
-  <si>
-    <t>Admin</t>
+    <t>Blue Legacy</t>
+  </si>
+  <si>
+    <t>Fixed Assets</t>
+  </si>
+  <si>
+    <t>Configuration</t>
+  </si>
+  <si>
+    <t>Bihaag</t>
+  </si>
+  <si>
+    <t>WiFi</t>
+  </si>
+  <si>
+    <t>C. Steinweg</t>
+  </si>
+  <si>
+    <t>Recruitment Work</t>
+  </si>
+  <si>
+    <t>Cubes</t>
+  </si>
+  <si>
+    <t>Brian</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>Conekt – Aurum</t>
+  </si>
+  <si>
+    <t>Team Meeting</t>
+  </si>
+  <si>
+    <t>Database</t>
+  </si>
+  <si>
+    <t>Conekt – Clientele</t>
+  </si>
+  <si>
+    <t>Recruitment team meeting</t>
+  </si>
+  <si>
+    <t>Demo</t>
   </si>
   <si>
     <t>Charles</t>
   </si>
   <si>
-    <t>Screening</t>
-  </si>
-  <si>
-    <t>Analysis</t>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Conekt – Internal Meeting</t>
+  </si>
+  <si>
+    <t>Deployment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charmane </t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Conekt – Meridian</t>
+  </si>
+  <si>
+    <t>Design</t>
+  </si>
+  <si>
+    <t>Clement</t>
+  </si>
+  <si>
+    <t>Conekt – Winning Business</t>
+  </si>
+  <si>
+    <t>Documentation</t>
+  </si>
+  <si>
+    <t>Diederik</t>
+  </si>
+  <si>
+    <t>Conekt AGSA SharePoint</t>
+  </si>
+  <si>
+    <t>Events</t>
+  </si>
+  <si>
+    <t>Diptendubala</t>
+  </si>
+  <si>
+    <t>Dentons</t>
+  </si>
+  <si>
+    <t>ETL</t>
+  </si>
+  <si>
+    <t>Dipthi</t>
+  </si>
+  <si>
+    <t>Discovery</t>
+  </si>
+  <si>
+    <t>FrontEnd</t>
+  </si>
+  <si>
+    <t>Edmond</t>
+  </si>
+  <si>
+    <t>Discovery Bank</t>
+  </si>
+  <si>
+    <t>Installing</t>
+  </si>
+  <si>
+    <t>Elijah</t>
+  </si>
+  <si>
+    <t>Discovery CRES</t>
+  </si>
+  <si>
+    <t>Elrida</t>
+  </si>
+  <si>
+    <t>Discovery CSI</t>
+  </si>
+  <si>
+    <t>Lunch</t>
+  </si>
+  <si>
+    <t>Engelina</t>
+  </si>
+  <si>
+    <t>Discovery Health</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Eugene</t>
+  </si>
+  <si>
+    <t>Discovery Information Governance and Security</t>
+  </si>
+  <si>
+    <t>Presenting</t>
+  </si>
+  <si>
+    <t>Evashan</t>
+  </si>
+  <si>
+    <t>Discovery Innovation Lab</t>
+  </si>
+  <si>
+    <t>Project Management</t>
+  </si>
+  <si>
+    <t>Example</t>
+  </si>
+  <si>
+    <t>Discovery People</t>
+  </si>
+  <si>
+    <t>Fayruz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discovery Skills </t>
+  </si>
+  <si>
+    <t>Sales call</t>
+  </si>
+  <si>
+    <t>Hamerl</t>
+  </si>
+  <si>
+    <t>Discovery Vitality</t>
+  </si>
+  <si>
+    <t>SharePoint</t>
+  </si>
+  <si>
+    <t>Ian</t>
+  </si>
+  <si>
+    <t>Gyro</t>
+  </si>
+  <si>
+    <t>Testing</t>
+  </si>
+  <si>
+    <t>Jabulane</t>
+  </si>
+  <si>
+    <t>KFC Digistics</t>
+  </si>
+  <si>
+    <t>Travel</t>
+  </si>
+  <si>
+    <t>Jashmeen</t>
+  </si>
+  <si>
+    <t>Life Healthcare</t>
+  </si>
+  <si>
+    <t>Troubleshooting</t>
+  </si>
+  <si>
+    <t>Joseph</t>
+  </si>
+  <si>
+    <t>Medi-Charge</t>
+  </si>
+  <si>
+    <t>Waiting on client</t>
+  </si>
+  <si>
+    <t>Juan</t>
+  </si>
+  <si>
+    <t>MICA Build</t>
+  </si>
+  <si>
+    <t>Website content</t>
+  </si>
+  <si>
+    <t>Jubhele</t>
+  </si>
+  <si>
+    <t>Michelin</t>
+  </si>
+  <si>
+    <t>Website and collateral</t>
+  </si>
+  <si>
+    <t>Karabo</t>
+  </si>
+  <si>
+    <t>Mistro Foods</t>
+  </si>
+  <si>
+    <t>Kavish</t>
+  </si>
+  <si>
+    <t>OK Furnitures</t>
+  </si>
+  <si>
+    <t>Sick leave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayden </t>
+  </si>
+  <si>
+    <t>Olympic Paints</t>
+  </si>
+  <si>
+    <t>Study Leave</t>
+  </si>
+  <si>
+    <t>Keown</t>
+  </si>
+  <si>
+    <t>RMB</t>
+  </si>
+  <si>
+    <t>Family Responsibility Leave</t>
+  </si>
+  <si>
+    <t>Kiaan</t>
+  </si>
+  <si>
+    <t>RMB CM Data Warehouse support</t>
+  </si>
+  <si>
+    <t>Birthday leave</t>
+  </si>
+  <si>
+    <t>Lutchman</t>
+  </si>
+  <si>
+    <t>RMB CORE NRTI</t>
+  </si>
+  <si>
+    <t>Lwazisile</t>
+  </si>
+  <si>
+    <t>RMB Tumelo</t>
+  </si>
+  <si>
+    <t>Sick Leave - half day</t>
+  </si>
+  <si>
+    <t>Muzuvukile</t>
+  </si>
+  <si>
+    <t>Sachar Mobile</t>
+  </si>
+  <si>
+    <t>Annual Leave - half day</t>
+  </si>
+  <si>
+    <t>Nagendra</t>
+  </si>
+  <si>
+    <t>Sanlam</t>
+  </si>
+  <si>
+    <t>Nathalia</t>
+  </si>
+  <si>
+    <t>SBV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ndivhudzannyi </t>
+  </si>
+  <si>
+    <t>Sibanya</t>
+  </si>
+  <si>
+    <t>Neo</t>
+  </si>
+  <si>
+    <t>Transport Holdings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pascal  </t>
+  </si>
+  <si>
+    <t>Pogiso</t>
+  </si>
+  <si>
+    <t>Pranav</t>
   </si>
   <si>
     <t>Ravi</t>
   </si>
   <si>
-    <t>Headhunting</t>
-  </si>
-  <si>
-    <t>Architecture</t>
-  </si>
-  <si>
-    <t>Interviews</t>
-  </si>
-  <si>
-    <t>Training</t>
-  </si>
-  <si>
-    <t>Joseph</t>
-  </si>
-  <si>
-    <t>Fixed Assets</t>
-  </si>
-  <si>
-    <t>Configuration</t>
-  </si>
-  <si>
-    <t>Recruitment Work</t>
-  </si>
-  <si>
-    <t>Cubes</t>
-  </si>
-  <si>
-    <t>Avinash</t>
-  </si>
-  <si>
-    <t>Team Meeting</t>
-  </si>
-  <si>
-    <t>Database</t>
-  </si>
-  <si>
-    <t>Recruitment team meeting</t>
-  </si>
-  <si>
-    <t>Demo</t>
-  </si>
-  <si>
-    <t>Deployment</t>
-  </si>
-  <si>
-    <t>Design</t>
-  </si>
-  <si>
-    <t>Documentation</t>
+    <t>Rivashan</t>
+  </si>
+  <si>
+    <t>Rushil</t>
   </si>
   <si>
     <t>Sanele</t>
   </si>
   <si>
-    <t>Events</t>
-  </si>
-  <si>
-    <t>Discovery</t>
-  </si>
-  <si>
-    <t>ETL</t>
-  </si>
-  <si>
-    <t>FrontEnd</t>
-  </si>
-  <si>
-    <t>Installing</t>
-  </si>
-  <si>
-    <t>Edmond</t>
-  </si>
-  <si>
-    <t>Meeting</t>
-  </si>
-  <si>
-    <t>Lunch</t>
-  </si>
-  <si>
-    <t>Other</t>
-  </si>
-  <si>
-    <t>Kavish</t>
-  </si>
-  <si>
-    <t>Presenting</t>
-  </si>
-  <si>
     <t>Shaila</t>
   </si>
   <si>
-    <t>Project Management</t>
-  </si>
-  <si>
-    <t>Research</t>
-  </si>
-  <si>
-    <t>Sales call</t>
-  </si>
-  <si>
-    <t>SharePoint</t>
-  </si>
-  <si>
-    <t>Testing</t>
-  </si>
-  <si>
-    <t>Travel</t>
-  </si>
-  <si>
-    <t>Eugene</t>
-  </si>
-  <si>
-    <t>Troubleshooting</t>
-  </si>
-  <si>
-    <t>Waiting on client</t>
-  </si>
-  <si>
-    <t>Aubrey</t>
-  </si>
-  <si>
-    <t>Michelin</t>
-  </si>
-  <si>
-    <t>Website content</t>
-  </si>
-  <si>
-    <t>Website and collateral</t>
-  </si>
-  <si>
-    <t>Annual Leave</t>
-  </si>
-  <si>
-    <t>Angela</t>
-  </si>
-  <si>
-    <t>OK Furnitures</t>
-  </si>
-  <si>
-    <t>Sick leave</t>
-  </si>
-  <si>
-    <t>Study Leave</t>
+    <t>Shaylin</t>
+  </si>
+  <si>
+    <t>Shriya</t>
   </si>
   <si>
     <t>Siemon</t>
   </si>
   <si>
-    <t>Family Responsibility Leave</t>
-  </si>
-  <si>
-    <t>Birthday leave</t>
-  </si>
-  <si>
-    <t>Public Holiday</t>
-  </si>
-  <si>
-    <t>Sachar Mobile</t>
-  </si>
-  <si>
-    <t>Sick Leave - half day</t>
+    <t>Suryansh</t>
+  </si>
+  <si>
+    <t>Teolan</t>
+  </si>
+  <si>
+    <t>Thapelo</t>
+  </si>
+  <si>
+    <t>Timothy</t>
+  </si>
+  <si>
+    <t>Tutu</t>
+  </si>
+  <si>
+    <t>Tyson</t>
+  </si>
+  <si>
+    <t>Vincent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yugeshin </t>
   </si>
   <si>
     <t>Zola</t>
   </si>
   <si>
-    <t>Total Billable Hours</t>
-  </si>
-  <si>
-    <t>Example</t>
-  </si>
-  <si>
-    <t>Engelina</t>
-  </si>
-  <si>
-    <t>Hamerl</t>
-  </si>
-  <si>
-    <t>SBV</t>
-  </si>
-  <si>
-    <t>Shaylin</t>
-  </si>
-  <si>
-    <t>Amanda</t>
-  </si>
-  <si>
-    <t>Ian</t>
-  </si>
-  <si>
-    <t>Work</t>
-  </si>
-  <si>
-    <t>ADVTech</t>
-  </si>
-  <si>
-    <t>Base 3</t>
-  </si>
-  <si>
-    <t>Dentons</t>
-  </si>
-  <si>
-    <t>Discovery People</t>
-  </si>
-  <si>
-    <t>Fayruz</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Vincent</t>
-  </si>
-  <si>
-    <t>Phone</t>
-  </si>
-  <si>
-    <t>WiFi</t>
-  </si>
-  <si>
-    <t>Internal Sambe</t>
-  </si>
-  <si>
-    <t>AFA Sasfin</t>
-  </si>
-  <si>
-    <t>Artist Proof Studio</t>
-  </si>
-  <si>
-    <t>C. Steinweg</t>
-  </si>
-  <si>
-    <t>Conekt AGSA SharePoint</t>
-  </si>
-  <si>
-    <t>Bihaag</t>
-  </si>
-  <si>
-    <t>Conekt – Meridian</t>
-  </si>
-  <si>
-    <t>Conekt – Clientele</t>
-  </si>
-  <si>
-    <t>Clement</t>
-  </si>
-  <si>
-    <t>Conekt – Winning Business</t>
-  </si>
-  <si>
-    <t>Conekt – Internal Meeting</t>
-  </si>
-  <si>
-    <t>Diederik</t>
-  </si>
-  <si>
-    <t>Diptendubala</t>
-  </si>
-  <si>
-    <t>Discovery Information Governance and Security</t>
-  </si>
-  <si>
-    <t>Elijah</t>
-  </si>
-  <si>
-    <t>Discovery Bank</t>
-  </si>
-  <si>
-    <t>Discovery CSI</t>
-  </si>
-  <si>
-    <t>Discovery Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discovery Skills </t>
-  </si>
-  <si>
-    <t>Discovery Vitality</t>
-  </si>
-  <si>
-    <t>Gyro</t>
-  </si>
-  <si>
-    <t>Juan</t>
-  </si>
-  <si>
-    <t>KFC Digistics</t>
-  </si>
-  <si>
-    <t>Medi-Charge</t>
-  </si>
-  <si>
-    <t>MICA Build</t>
-  </si>
-  <si>
-    <t>Mistro Foods</t>
-  </si>
-  <si>
-    <t>Olympic Paints</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ndivhudzannyi </t>
-  </si>
-  <si>
-    <t>RMB CM Data Warehouse support</t>
-  </si>
-  <si>
-    <t>RMB CORE NRTI</t>
-  </si>
-  <si>
-    <t>Pranav</t>
-  </si>
-  <si>
-    <t>RMB Tumelo</t>
-  </si>
-  <si>
-    <t>Rivashan</t>
-  </si>
-  <si>
-    <t>Sibanya</t>
-  </si>
-  <si>
-    <t>Transport Holdings</t>
-  </si>
-  <si>
-    <t>Timothy</t>
-  </si>
-  <si>
-    <t>Tutu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yugeshin </t>
-  </si>
-  <si>
-    <t>Nagendra</t>
-  </si>
-  <si>
-    <t>Tyson</t>
-  </si>
-  <si>
-    <t>Worker's Day</t>
-  </si>
-  <si>
-    <t>Brian</t>
-  </si>
-  <si>
-    <t>Jubhele</t>
-  </si>
-  <si>
-    <t>Evashan</t>
-  </si>
-  <si>
-    <t>Karabo</t>
-  </si>
-  <si>
-    <t>Keown</t>
-  </si>
-  <si>
-    <t>Kiaan</t>
-  </si>
-  <si>
-    <t>Muzuvukile</t>
-  </si>
-  <si>
-    <t>Nathalia</t>
-  </si>
-  <si>
-    <t>Neo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pascal  </t>
-  </si>
-  <si>
-    <t>Thapelo</t>
-  </si>
-  <si>
-    <t>Sanlam</t>
-  </si>
-  <si>
-    <t>Life Healthcare</t>
-  </si>
-  <si>
-    <t>Elrida</t>
-  </si>
-  <si>
-    <t>Jashmeen</t>
-  </si>
-  <si>
-    <t>Pogiso</t>
-  </si>
-  <si>
-    <t>Suryansh</t>
-  </si>
-  <si>
-    <t>Dipthi</t>
-  </si>
-  <si>
-    <t>Lutchman</t>
-  </si>
-  <si>
-    <t>Buhle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charmane </t>
-  </si>
-  <si>
-    <t>Jabulane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kayden </t>
-  </si>
-  <si>
-    <t>Lwazisile</t>
-  </si>
-  <si>
-    <t>Rushil</t>
-  </si>
-  <si>
-    <t>Shriya</t>
-  </si>
-  <si>
-    <t>Teolan</t>
-  </si>
-  <si>
-    <t>Discovery CRES</t>
-  </si>
-  <si>
-    <t>Annual Leave - half day</t>
-  </si>
-  <si>
-    <t>RMB</t>
-  </si>
-  <si>
-    <t>Discovery Innovation Lab</t>
-  </si>
-  <si>
-    <t>Conekt – Aurum</t>
-  </si>
-  <si>
-    <t>Assimil8</t>
-  </si>
-  <si>
-    <t>Blue Legacy</t>
-  </si>
-  <si>
     <t>Resham</t>
-  </si>
-  <si>
-    <t>Discovery Induction</t>
-  </si>
-  <si>
-    <t>Attended high performers standup</t>
-  </si>
-  <si>
-    <t>Attended high performers retrospective meeting</t>
-  </si>
-  <si>
-    <t>Attended midday check-in</t>
-  </si>
-  <si>
-    <t>Udemy - Ms SQL Server DBA</t>
-  </si>
-  <si>
-    <t>Attended team meeting</t>
-  </si>
-  <si>
-    <t>Udemy - SSIS Introduction</t>
-  </si>
-  <si>
-    <t>Client Communication</t>
-  </si>
-  <si>
-    <t>Udemy - Ms SQL Server T-SQL</t>
-  </si>
-  <si>
-    <t>Presentation - Dashboard</t>
   </si>
 </sst>
 </file>
@@ -641,7 +641,7 @@
     <numFmt numFmtId="164" formatCode="[h]:mm"/>
     <numFmt numFmtId="165" formatCode="h:mm;@"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1341,118 +1341,6 @@
   </cellStyles>
   <dxfs count="23">
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -1593,6 +1481,118 @@
         <scheme val="none"/>
       </font>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{6758C6CA-2356-4535-9D9D-86230C423211}"/>
@@ -1658,26 +1658,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2E876225-7964-4082-91F1-C6221C464408}" name="WorkType" displayName="WorkType" ref="H2:H76" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2E876225-7964-4082-91F1-C6221C464408}" name="WorkType" displayName="WorkType" ref="H2:H76" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="H2:H76" xr:uid="{2E876225-7964-4082-91F1-C6221C464408}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H3:H76">
     <sortCondition ref="H64:H76"/>
   </sortState>
   <tableColumns count="1">
-    <tableColumn id="2" xr3:uid="{234A6588-4DEA-4067-9367-AEAFE02CA40D}" name="Resource" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{234A6588-4DEA-4067-9367-AEAFE02CA40D}" name="Resource" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B149CFBE-03DA-4A5C-8F86-52A53133C863}" name="ProjectTable" displayName="ProjectTable" ref="F2:F40" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18" tableBorderDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B149CFBE-03DA-4A5C-8F86-52A53133C863}" name="ProjectTable" displayName="ProjectTable" ref="F2:F40" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2" tableBorderDxfId="1">
   <autoFilter ref="F2:F40" xr:uid="{B149CFBE-03DA-4A5C-8F86-52A53133C863}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="F3:F19">
     <sortCondition ref="F2:F19"/>
   </sortState>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{D9788319-59C4-447A-9364-6F4EF6730453}" name="Description" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{D9788319-59C4-447A-9364-6F4EF6730453}" name="Description" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1954,30 +1954,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{451FE93A-CBFB-4D27-9D4A-1E2332DAE6F0}">
   <dimension ref="A5:J120"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12" style="21" customWidth="1"/>
-    <col min="2" max="2" width="13.09765625" style="21" customWidth="1"/>
-    <col min="3" max="3" width="16.19921875" style="21" customWidth="1"/>
+    <col min="2" max="2" width="13.125" style="21" customWidth="1"/>
+    <col min="3" max="3" width="16.25" style="21" customWidth="1"/>
     <col min="4" max="5" width="20" style="21" customWidth="1"/>
-    <col min="6" max="6" width="23.09765625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="23.125" style="21" customWidth="1"/>
     <col min="7" max="7" width="34" style="21" customWidth="1"/>
-    <col min="8" max="16384" width="8.69921875" style="21"/>
+    <col min="8" max="16384" width="8.75" style="21"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="A5" s="35" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>172</v>
+        <v>1</v>
       </c>
       <c r="C5" s="35"/>
       <c r="H5" s="38"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="A6" s="35" t="s">
-        <v>93</v>
+        <v>2</v>
       </c>
       <c r="B6" s="68">
         <f>F115</f>
@@ -1989,60 +1989,60 @@
       <c r="H6" s="38"/>
       <c r="J6" s="39"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="H7" s="38"/>
     </row>
-    <row r="8" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="25.15">
       <c r="A8" s="22" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F8" s="23" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G8" s="40" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I8" s="24" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J8" s="41" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="45">
         <v>46143</v>
       </c>
       <c r="B9" s="45" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C9" s="46" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D9" s="46"/>
       <c r="E9" s="46" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="F9" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G9" s="47" t="s">
-        <v>152</v>
+        <v>17</v>
       </c>
       <c r="H9" s="48">
         <f t="shared" ref="H9:H110" si="0">J9-I9</f>
@@ -2055,12 +2055,12 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10">
       <c r="A10" s="29">
         <v>46144</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C10" s="30"/>
       <c r="D10" s="30"/>
@@ -2074,12 +2074,12 @@
       <c r="I10" s="33"/>
       <c r="J10" s="33"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10">
       <c r="A11" s="29">
         <v>46145</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C11" s="30"/>
       <c r="D11" s="30"/>
@@ -2093,25 +2093,25 @@
       <c r="I11" s="33"/>
       <c r="J11" s="33"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10">
       <c r="A12" s="20">
         <v>46146</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D12" s="25"/>
       <c r="E12" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G12" s="26" t="s">
-        <v>188</v>
+        <v>22</v>
       </c>
       <c r="H12" s="27">
         <f t="shared" si="0"/>
@@ -2124,25 +2124,25 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10">
       <c r="A13" s="20">
         <v>46147</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D13" s="25"/>
       <c r="E13" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G13" s="26" t="s">
-        <v>188</v>
+        <v>22</v>
       </c>
       <c r="H13" s="27">
         <f t="shared" si="0"/>
@@ -2155,25 +2155,25 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10">
       <c r="A14" s="20">
         <v>46148</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D14" s="25"/>
       <c r="E14" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G14" s="26" t="s">
-        <v>188</v>
+        <v>22</v>
       </c>
       <c r="H14" s="27">
         <f t="shared" si="0"/>
@@ -2186,25 +2186,25 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="A15" s="20">
         <v>46149</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D15" s="25"/>
       <c r="E15" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F15" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G15" s="26" t="s">
-        <v>188</v>
+        <v>22</v>
       </c>
       <c r="H15" s="27">
         <f>J15-I15</f>
@@ -2217,25 +2217,25 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10">
       <c r="A16" s="20">
         <v>46150</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D16" s="25"/>
       <c r="E16" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F16" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G16" s="26" t="s">
-        <v>188</v>
+        <v>22</v>
       </c>
       <c r="H16" s="27">
         <f t="shared" si="0"/>
@@ -2248,12 +2248,12 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10">
       <c r="A17" s="29">
         <v>46151</v>
       </c>
       <c r="B17" s="29" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C17" s="30"/>
       <c r="D17" s="30"/>
@@ -2267,12 +2267,12 @@
       <c r="I17" s="33"/>
       <c r="J17" s="33"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10">
       <c r="A18" s="29">
         <v>46152</v>
       </c>
       <c r="B18" s="29" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C18" s="30"/>
       <c r="D18" s="30"/>
@@ -2286,25 +2286,25 @@
       <c r="I18" s="33"/>
       <c r="J18" s="33"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10">
       <c r="A19" s="20">
         <v>46153</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C19" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D19" s="25"/>
       <c r="E19" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F19" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G19" s="26" t="s">
-        <v>189</v>
+        <v>26</v>
       </c>
       <c r="H19" s="27">
         <f t="shared" si="0"/>
@@ -2317,25 +2317,25 @@
         <v>0.34027777777777779</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10">
       <c r="A20" s="20">
         <v>46153</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D20" s="25"/>
       <c r="E20" s="25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F20" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G20" s="26" t="s">
-        <v>192</v>
+        <v>28</v>
       </c>
       <c r="H20" s="27">
         <f t="shared" si="0"/>
@@ -2348,25 +2348,25 @@
         <v>0.375</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10">
       <c r="A21" s="20">
         <v>46153</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D21" s="25"/>
       <c r="E21" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F21" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G21" s="26" t="s">
-        <v>193</v>
+        <v>29</v>
       </c>
       <c r="H21" s="27">
         <f t="shared" si="0"/>
@@ -2379,25 +2379,25 @@
         <v>0.38819444444444445</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10">
       <c r="A22" s="20">
         <v>46153</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D22" s="25"/>
       <c r="E22" s="25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F22" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G22" s="26" t="s">
-        <v>192</v>
+        <v>28</v>
       </c>
       <c r="H22" s="27">
         <f t="shared" si="0"/>
@@ -2410,25 +2410,25 @@
         <v>0.4548611111111111</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10">
       <c r="A23" s="20">
         <v>46153</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C23" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D23" s="25"/>
       <c r="E23" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F23" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G23" s="26" t="s">
-        <v>191</v>
+        <v>30</v>
       </c>
       <c r="H23" s="27">
         <f t="shared" si="0"/>
@@ -2441,25 +2441,25 @@
         <v>0.48055555555555557</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10">
       <c r="A24" s="20">
         <v>46153</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D24" s="25"/>
       <c r="E24" s="25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F24" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G24" s="26" t="s">
-        <v>192</v>
+        <v>28</v>
       </c>
       <c r="H24" s="27">
         <f t="shared" si="0"/>
@@ -2472,25 +2472,25 @@
         <v>0.53819444444444442</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10">
       <c r="A25" s="20">
         <v>46153</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D25" s="25"/>
       <c r="E25" s="25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F25" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G25" s="26" t="s">
-        <v>192</v>
+        <v>28</v>
       </c>
       <c r="H25" s="27">
         <f t="shared" si="0"/>
@@ -2503,25 +2503,25 @@
         <v>0.66319444444444442</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" ht="25.15">
       <c r="A26" s="20">
         <v>46153</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D26" s="25"/>
       <c r="E26" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F26" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G26" s="26" t="s">
-        <v>190</v>
+        <v>31</v>
       </c>
       <c r="H26" s="27">
         <f t="shared" si="0"/>
@@ -2534,25 +2534,25 @@
         <v>0.71666666666666667</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10">
       <c r="A27" s="20">
         <v>46154</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D27" s="25"/>
       <c r="E27" s="25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F27" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G27" s="26" t="s">
-        <v>192</v>
+        <v>28</v>
       </c>
       <c r="H27" s="27">
         <f t="shared" si="0"/>
@@ -2565,25 +2565,25 @@
         <v>0.4548611111111111</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10">
       <c r="A28" s="20">
         <v>46154</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C28" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D28" s="25"/>
       <c r="E28" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F28" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G28" s="26" t="s">
-        <v>191</v>
+        <v>30</v>
       </c>
       <c r="H28" s="27">
         <f t="shared" si="0"/>
@@ -2596,25 +2596,25 @@
         <v>0.49513888888888891</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10">
       <c r="A29" s="20">
         <v>46154</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C29" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D29" s="25"/>
       <c r="E29" s="25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F29" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G29" s="26" t="s">
-        <v>192</v>
+        <v>28</v>
       </c>
       <c r="H29" s="27">
         <f t="shared" si="0"/>
@@ -2627,25 +2627,25 @@
         <v>0.53819444444444442</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10">
       <c r="A30" s="20">
         <v>46154</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C30" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D30" s="25"/>
       <c r="E30" s="25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F30" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G30" s="26" t="s">
-        <v>192</v>
+        <v>28</v>
       </c>
       <c r="H30" s="27">
         <f t="shared" si="0"/>
@@ -2658,25 +2658,25 @@
         <v>0.66319444444444442</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" ht="25.15">
       <c r="A31" s="20">
         <v>46154</v>
       </c>
       <c r="B31" s="20" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C31" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D31" s="25"/>
       <c r="E31" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F31" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G31" s="26" t="s">
-        <v>190</v>
+        <v>31</v>
       </c>
       <c r="H31" s="27">
         <f t="shared" si="0"/>
@@ -2689,25 +2689,25 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10">
       <c r="A32" s="20">
         <v>46155</v>
       </c>
       <c r="B32" s="20" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C32" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D32" s="25"/>
       <c r="E32" s="25" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="F32" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G32" s="26" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="H32" s="27">
         <f t="shared" si="0"/>
@@ -2720,25 +2720,25 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10">
       <c r="A33" s="20">
         <v>46156</v>
       </c>
       <c r="B33" s="20" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D33" s="25"/>
       <c r="E33" s="25" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="F33" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G33" s="26" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="H33" s="27">
         <f t="shared" si="0"/>
@@ -2751,25 +2751,25 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10">
       <c r="A34" s="20">
         <v>46157</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C34" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D34" s="25"/>
       <c r="E34" s="25" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="F34" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G34" s="26" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="H34" s="27">
         <f t="shared" si="0"/>
@@ -2782,12 +2782,12 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10">
       <c r="A35" s="29">
         <v>46158</v>
       </c>
       <c r="B35" s="29" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C35" s="30"/>
       <c r="D35" s="30"/>
@@ -2801,12 +2801,12 @@
       <c r="I35" s="33"/>
       <c r="J35" s="33"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10">
       <c r="A36" s="29">
         <v>46159</v>
       </c>
       <c r="B36" s="29" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C36" s="30"/>
       <c r="D36" s="30"/>
@@ -2820,25 +2820,25 @@
       <c r="I36" s="33"/>
       <c r="J36" s="33"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10">
       <c r="A37" s="20">
         <v>46160</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C37" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D37" s="25"/>
       <c r="E37" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F37" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G37" s="26" t="s">
-        <v>189</v>
+        <v>26</v>
       </c>
       <c r="H37" s="27">
         <f t="shared" si="0"/>
@@ -2851,25 +2851,25 @@
         <v>0.35138888888888886</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10">
       <c r="A38" s="20">
         <v>46160</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C38" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D38" s="25"/>
       <c r="E38" s="25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F38" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G38" s="26" t="s">
-        <v>192</v>
+        <v>28</v>
       </c>
       <c r="H38" s="27">
         <f t="shared" si="0"/>
@@ -2882,25 +2882,25 @@
         <v>0.4548611111111111</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10">
       <c r="A39" s="20">
         <v>46160</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C39" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D39" s="25"/>
       <c r="E39" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F39" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G39" s="26" t="s">
-        <v>191</v>
+        <v>30</v>
       </c>
       <c r="H39" s="27">
         <f t="shared" si="0"/>
@@ -2913,25 +2913,25 @@
         <v>0.47916666666666669</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10">
       <c r="A40" s="20">
         <v>46160</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C40" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D40" s="25"/>
       <c r="E40" s="25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F40" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G40" s="26" t="s">
-        <v>192</v>
+        <v>28</v>
       </c>
       <c r="H40" s="27">
         <f t="shared" si="0"/>
@@ -2944,25 +2944,25 @@
         <v>0.53472222222222221</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10">
       <c r="A41" s="20">
         <v>46160</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C41" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D41" s="25"/>
       <c r="E41" s="25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F41" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G41" s="26" t="s">
-        <v>192</v>
+        <v>28</v>
       </c>
       <c r="H41" s="27">
         <f t="shared" si="0"/>
@@ -2975,25 +2975,25 @@
         <v>0.66319444444444442</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" ht="25.15">
       <c r="A42" s="20">
         <v>46160</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C42" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D42" s="25"/>
       <c r="E42" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F42" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G42" s="26" t="s">
-        <v>190</v>
+        <v>31</v>
       </c>
       <c r="H42" s="27">
         <f t="shared" si="0"/>
@@ -3006,25 +3006,25 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10">
       <c r="A43" s="20">
         <v>46161</v>
       </c>
       <c r="B43" s="20" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C43" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D43" s="25"/>
       <c r="E43" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F43" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G43" s="26" t="s">
-        <v>189</v>
+        <v>26</v>
       </c>
       <c r="H43" s="27">
         <f t="shared" si="0"/>
@@ -3037,52 +3037,56 @@
         <v>0.34166666666666667</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10">
       <c r="A44" s="20">
         <v>46161</v>
       </c>
       <c r="B44" s="20" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C44" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D44" s="25"/>
       <c r="E44" s="25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F44" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G44" s="26" t="s">
-        <v>192</v>
+        <v>28</v>
       </c>
       <c r="H44" s="27">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I44" s="28"/>
-      <c r="J44" s="28"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+        <v>0.11319444444444443</v>
+      </c>
+      <c r="I44" s="28">
+        <v>0.34166666666666667</v>
+      </c>
+      <c r="J44" s="28">
+        <v>0.4548611111111111</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
       <c r="A45" s="20">
         <v>46161</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C45" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D45" s="25"/>
       <c r="E45" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F45" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G45" s="26" t="s">
-        <v>191</v>
+        <v>30</v>
       </c>
       <c r="H45" s="27">
         <f t="shared" si="0"/>
@@ -3095,25 +3099,25 @@
         <v>0.46527777777777779</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10">
       <c r="A46" s="20">
         <v>46161</v>
       </c>
       <c r="B46" s="20" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C46" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D46" s="25"/>
       <c r="E46" s="25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F46" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G46" s="26" t="s">
-        <v>192</v>
+        <v>28</v>
       </c>
       <c r="H46" s="27">
         <f t="shared" si="0"/>
@@ -3126,25 +3130,25 @@
         <v>0.53125</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10">
       <c r="A47" s="20">
         <v>46161</v>
       </c>
       <c r="B47" s="20" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C47" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D47" s="25"/>
       <c r="E47" s="25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F47" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G47" s="26" t="s">
-        <v>192</v>
+        <v>28</v>
       </c>
       <c r="H47" s="27">
         <f t="shared" si="0"/>
@@ -3157,25 +3161,25 @@
         <v>0.66319444444444442</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" ht="25.15">
       <c r="A48" s="20">
         <v>46161</v>
       </c>
       <c r="B48" s="20" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C48" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D48" s="25"/>
       <c r="E48" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F48" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G48" s="26" t="s">
-        <v>190</v>
+        <v>31</v>
       </c>
       <c r="H48" s="27">
         <f t="shared" si="0"/>
@@ -3188,25 +3192,25 @@
         <v>0.7104166666666667</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10">
       <c r="A49" s="20">
         <v>46162</v>
       </c>
       <c r="B49" s="20" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C49" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D49" s="25"/>
       <c r="E49" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F49" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G49" s="26" t="s">
-        <v>189</v>
+        <v>26</v>
       </c>
       <c r="H49" s="27">
         <f t="shared" si="0"/>
@@ -3219,25 +3223,25 @@
         <v>0.34375</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10">
       <c r="A50" s="20">
         <v>46162</v>
       </c>
       <c r="B50" s="20" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C50" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D50" s="25"/>
       <c r="E50" s="25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F50" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G50" s="26" t="s">
-        <v>192</v>
+        <v>28</v>
       </c>
       <c r="H50" s="27">
         <f t="shared" si="0"/>
@@ -3250,25 +3254,25 @@
         <v>0.4548611111111111</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10">
       <c r="A51" s="20">
         <v>46162</v>
       </c>
       <c r="B51" s="20" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C51" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D51" s="25"/>
       <c r="E51" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F51" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G51" s="26" t="s">
-        <v>191</v>
+        <v>30</v>
       </c>
       <c r="H51" s="27">
         <f t="shared" si="0"/>
@@ -3281,25 +3285,25 @@
         <v>0.46388888888888891</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10">
       <c r="A52" s="20">
         <v>46162</v>
       </c>
       <c r="B52" s="20" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C52" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D52" s="25"/>
       <c r="E52" s="25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F52" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G52" s="26" t="s">
-        <v>192</v>
+        <v>28</v>
       </c>
       <c r="H52" s="27">
         <f t="shared" si="0"/>
@@ -3312,25 +3316,25 @@
         <v>0.53472222222222221</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10">
       <c r="A53" s="20">
         <v>46162</v>
       </c>
       <c r="B53" s="20" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C53" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D53" s="25"/>
       <c r="E53" s="25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F53" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G53" s="26" t="s">
-        <v>194</v>
+        <v>33</v>
       </c>
       <c r="H53" s="27">
         <f t="shared" si="0"/>
@@ -3343,25 +3347,25 @@
         <v>0.58333333333333337</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10">
       <c r="A54" s="20">
         <v>46162</v>
       </c>
       <c r="B54" s="20" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C54" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D54" s="25"/>
       <c r="E54" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F54" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G54" s="26" t="s">
-        <v>193</v>
+        <v>29</v>
       </c>
       <c r="H54" s="27">
         <f t="shared" si="0"/>
@@ -3374,25 +3378,25 @@
         <v>0.65138888888888891</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10" ht="25.15">
       <c r="A55" s="20">
         <v>46162</v>
       </c>
       <c r="B55" s="20" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C55" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D55" s="25"/>
       <c r="E55" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F55" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G55" s="26" t="s">
-        <v>190</v>
+        <v>31</v>
       </c>
       <c r="H55" s="27">
         <f t="shared" si="0"/>
@@ -3405,25 +3409,25 @@
         <v>0.67291666666666672</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10">
       <c r="A56" s="20">
         <v>46162</v>
       </c>
       <c r="B56" s="20" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C56" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D56" s="25"/>
       <c r="E56" s="25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F56" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G56" s="26" t="s">
-        <v>194</v>
+        <v>33</v>
       </c>
       <c r="H56" s="27">
         <f t="shared" si="0"/>
@@ -3436,25 +3440,25 @@
         <v>0.71250000000000002</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10">
       <c r="A57" s="20">
         <v>46163</v>
       </c>
       <c r="B57" s="20" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C57" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D57" s="25"/>
       <c r="E57" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F57" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G57" s="26" t="s">
-        <v>189</v>
+        <v>26</v>
       </c>
       <c r="H57" s="27">
         <f t="shared" si="0"/>
@@ -3467,25 +3471,25 @@
         <v>0.34166666666666667</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10">
       <c r="A58" s="20">
         <v>46163</v>
       </c>
       <c r="B58" s="20" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C58" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D58" s="25"/>
       <c r="E58" s="25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F58" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G58" s="26" t="s">
-        <v>194</v>
+        <v>33</v>
       </c>
       <c r="H58" s="27">
         <f t="shared" si="0"/>
@@ -3498,25 +3502,25 @@
         <v>0.4548611111111111</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10">
       <c r="A59" s="20">
         <v>46163</v>
       </c>
       <c r="B59" s="20" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C59" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D59" s="25"/>
       <c r="E59" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F59" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G59" s="26" t="s">
-        <v>191</v>
+        <v>30</v>
       </c>
       <c r="H59" s="27">
         <f t="shared" si="0"/>
@@ -3529,25 +3533,25 @@
         <v>0.47013888888888888</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10">
       <c r="A60" s="20">
         <v>46163</v>
       </c>
       <c r="B60" s="20" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C60" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D60" s="25"/>
       <c r="E60" s="25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F60" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G60" s="26" t="s">
-        <v>194</v>
+        <v>33</v>
       </c>
       <c r="H60" s="27">
         <f t="shared" si="0"/>
@@ -3560,25 +3564,25 @@
         <v>0.53472222222222221</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10">
       <c r="A61" s="20">
         <v>46163</v>
       </c>
       <c r="B61" s="20" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C61" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D61" s="25"/>
       <c r="E61" s="25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F61" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G61" s="26" t="s">
-        <v>194</v>
+        <v>33</v>
       </c>
       <c r="H61" s="27">
         <f t="shared" si="0"/>
@@ -3591,25 +3595,25 @@
         <v>0.66319444444444442</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" ht="25.15">
       <c r="A62" s="20">
         <v>46163</v>
       </c>
       <c r="B62" s="20" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C62" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D62" s="25"/>
       <c r="E62" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F62" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G62" s="26" t="s">
-        <v>190</v>
+        <v>31</v>
       </c>
       <c r="H62" s="27">
         <f>J62-I62</f>
@@ -3622,25 +3626,25 @@
         <v>0.71597222222222223</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10">
       <c r="A63" s="20">
         <v>46164</v>
       </c>
       <c r="B63" s="20" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C63" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D63" s="25"/>
       <c r="E63" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F63" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G63" s="26" t="s">
-        <v>189</v>
+        <v>26</v>
       </c>
       <c r="H63" s="27">
         <f t="shared" ref="H63:H68" si="2">J63-I63</f>
@@ -3653,25 +3657,25 @@
         <v>0.34930555555555554</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10">
       <c r="A64" s="20">
         <v>46164</v>
       </c>
       <c r="B64" s="20" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C64" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D64" s="25"/>
       <c r="E64" s="25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F64" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G64" s="26" t="s">
-        <v>194</v>
+        <v>33</v>
       </c>
       <c r="H64" s="27">
         <f t="shared" si="2"/>
@@ -3684,25 +3688,25 @@
         <v>0.4548611111111111</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:10">
       <c r="A65" s="20">
         <v>46164</v>
       </c>
       <c r="B65" s="20" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C65" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D65" s="25"/>
       <c r="E65" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F65" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G65" s="26" t="s">
-        <v>191</v>
+        <v>30</v>
       </c>
       <c r="H65" s="27">
         <f t="shared" si="2"/>
@@ -3715,25 +3719,25 @@
         <v>0.48055555555555557</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10">
       <c r="A66" s="20">
         <v>46164</v>
       </c>
       <c r="B66" s="20" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C66" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D66" s="25"/>
       <c r="E66" s="25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F66" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G66" s="26" t="s">
-        <v>194</v>
+        <v>33</v>
       </c>
       <c r="H66" s="27">
         <f t="shared" si="2"/>
@@ -3746,25 +3750,25 @@
         <v>0.53819444444444442</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:10">
       <c r="A67" s="20">
         <v>46164</v>
       </c>
       <c r="B67" s="20" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C67" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D67" s="25"/>
       <c r="E67" s="25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F67" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G67" s="21" t="s">
-        <v>194</v>
+        <v>33</v>
       </c>
       <c r="H67" s="27">
         <f t="shared" si="2"/>
@@ -3777,25 +3781,25 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:10">
       <c r="A68" s="20">
         <v>46164</v>
       </c>
       <c r="B68" s="20" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C68" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D68" s="25"/>
       <c r="E68" s="25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F68" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G68" s="26" t="s">
-        <v>195</v>
+        <v>34</v>
       </c>
       <c r="H68" s="27">
         <f t="shared" si="2"/>
@@ -3808,25 +3812,25 @@
         <v>0.66319444444444442</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:10" ht="25.15">
       <c r="A69" s="20">
         <v>46164</v>
       </c>
       <c r="B69" s="20" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C69" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D69" s="25"/>
       <c r="E69" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F69" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G69" s="26" t="s">
-        <v>190</v>
+        <v>31</v>
       </c>
       <c r="H69" s="27">
         <f t="shared" si="0"/>
@@ -3839,12 +3843,12 @@
         <v>0.72916666666666663</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:10">
       <c r="A70" s="29">
         <v>46165</v>
       </c>
       <c r="B70" s="29" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C70" s="30"/>
       <c r="D70" s="30"/>
@@ -3858,12 +3862,12 @@
       <c r="I70" s="33"/>
       <c r="J70" s="33"/>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:10">
       <c r="A71" s="29">
         <v>46166</v>
       </c>
       <c r="B71" s="29" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C71" s="30"/>
       <c r="D71" s="30"/>
@@ -3877,25 +3881,25 @@
       <c r="I71" s="33"/>
       <c r="J71" s="33"/>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:10">
       <c r="A72" s="20">
         <v>46167</v>
       </c>
       <c r="B72" s="20" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C72" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D72" s="25"/>
       <c r="E72" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F72" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G72" s="26" t="s">
-        <v>189</v>
+        <v>26</v>
       </c>
       <c r="H72" s="27">
         <f t="shared" si="0"/>
@@ -3908,25 +3912,25 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:10">
       <c r="A73" s="20">
         <v>46167</v>
       </c>
       <c r="B73" s="20" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C73" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D73" s="25"/>
       <c r="E73" s="25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F73" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G73" s="26" t="s">
-        <v>196</v>
+        <v>35</v>
       </c>
       <c r="H73" s="27">
         <f t="shared" si="0"/>
@@ -3939,25 +3943,25 @@
         <v>0.4548611111111111</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:10">
       <c r="A74" s="20">
         <v>46167</v>
       </c>
       <c r="B74" s="20" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C74" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D74" s="25"/>
       <c r="E74" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F74" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G74" s="26" t="s">
-        <v>191</v>
+        <v>30</v>
       </c>
       <c r="H74" s="27">
         <f t="shared" si="0"/>
@@ -3970,25 +3974,25 @@
         <v>0.48680555555555555</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:10">
       <c r="A75" s="20">
         <v>46167</v>
       </c>
       <c r="B75" s="20" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C75" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D75" s="25"/>
       <c r="E75" s="25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F75" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G75" s="26" t="s">
-        <v>196</v>
+        <v>35</v>
       </c>
       <c r="H75" s="27">
         <f t="shared" si="0"/>
@@ -4001,25 +4005,25 @@
         <v>0.53819444444444442</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:10">
       <c r="A76" s="20">
         <v>46167</v>
       </c>
       <c r="B76" s="20" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C76" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D76" s="25"/>
       <c r="E76" s="25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F76" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G76" s="26" t="s">
-        <v>196</v>
+        <v>35</v>
       </c>
       <c r="H76" s="27">
         <f t="shared" si="0"/>
@@ -4032,25 +4036,25 @@
         <v>0.60416666666666663</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:10">
       <c r="A77" s="20">
         <v>46167</v>
       </c>
       <c r="B77" s="20" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C77" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D77" s="25"/>
       <c r="E77" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F77" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G77" s="26" t="s">
-        <v>193</v>
+        <v>29</v>
       </c>
       <c r="H77" s="27">
         <f t="shared" si="0"/>
@@ -4063,25 +4067,25 @@
         <v>0.66319444444444442</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:10" ht="25.15">
       <c r="A78" s="20">
         <v>46167</v>
       </c>
       <c r="B78" s="20" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C78" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D78" s="25"/>
       <c r="E78" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F78" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G78" s="26" t="s">
-        <v>190</v>
+        <v>31</v>
       </c>
       <c r="H78" s="27">
         <f t="shared" si="0"/>
@@ -4094,25 +4098,25 @@
         <v>0.71875</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:10">
       <c r="A79" s="20">
         <v>46168</v>
       </c>
       <c r="B79" s="20" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C79" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D79" s="25"/>
       <c r="E79" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F79" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G79" s="26" t="s">
-        <v>189</v>
+        <v>26</v>
       </c>
       <c r="H79" s="27">
         <f t="shared" si="0"/>
@@ -4125,25 +4129,25 @@
         <v>0.34166666666666667</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:10">
       <c r="A80" s="20">
         <v>46168</v>
       </c>
       <c r="B80" s="20" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C80" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D80" s="25"/>
       <c r="E80" s="25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F80" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G80" s="26" t="s">
-        <v>196</v>
+        <v>35</v>
       </c>
       <c r="H80" s="27">
         <f t="shared" si="0"/>
@@ -4156,25 +4160,25 @@
         <v>0.4548611111111111</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:10">
       <c r="A81" s="20">
         <v>46168</v>
       </c>
       <c r="B81" s="20" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C81" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D81" s="25"/>
       <c r="E81" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F81" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G81" s="26" t="s">
-        <v>191</v>
+        <v>30</v>
       </c>
       <c r="H81" s="27">
         <f t="shared" si="0"/>
@@ -4187,25 +4191,25 @@
         <v>0.49930555555555556</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:10">
       <c r="A82" s="20">
         <v>46168</v>
       </c>
       <c r="B82" s="20" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C82" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D82" s="25"/>
       <c r="E82" s="25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F82" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G82" s="26" t="s">
-        <v>196</v>
+        <v>35</v>
       </c>
       <c r="H82" s="27">
         <f t="shared" si="0"/>
@@ -4218,25 +4222,25 @@
         <v>0.53819444444444442</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:10">
       <c r="A83" s="20">
         <v>46168</v>
       </c>
       <c r="B83" s="20" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C83" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D83" s="25"/>
       <c r="E83" s="25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F83" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G83" s="26" t="s">
-        <v>196</v>
+        <v>35</v>
       </c>
       <c r="H83" s="27">
         <f t="shared" si="0"/>
@@ -4249,25 +4253,25 @@
         <v>0.60416666666666663</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:10">
       <c r="A84" s="20">
         <v>46168</v>
       </c>
       <c r="B84" s="20" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C84" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D84" s="25"/>
       <c r="E84" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F84" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G84" s="26" t="s">
-        <v>193</v>
+        <v>29</v>
       </c>
       <c r="H84" s="27">
         <f t="shared" si="0"/>
@@ -4280,25 +4284,25 @@
         <v>0.66319444444444442</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:10" ht="25.15">
       <c r="A85" s="20">
         <v>46168</v>
       </c>
       <c r="B85" s="20" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C85" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D85" s="25"/>
       <c r="E85" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F85" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G85" s="26" t="s">
-        <v>190</v>
+        <v>31</v>
       </c>
       <c r="H85" s="27">
         <f t="shared" si="0"/>
@@ -4311,25 +4315,25 @@
         <v>0.71180555555555558</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:10">
       <c r="A86" s="20">
         <v>46169</v>
       </c>
       <c r="B86" s="20" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C86" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D86" s="25"/>
       <c r="E86" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F86" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G86" s="26" t="s">
-        <v>189</v>
+        <v>26</v>
       </c>
       <c r="H86" s="27">
         <f t="shared" si="0"/>
@@ -4342,25 +4346,25 @@
         <v>0.34027777777777779</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:10">
       <c r="A87" s="20">
         <v>46169</v>
       </c>
       <c r="B87" s="20" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C87" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D87" s="25"/>
       <c r="E87" s="25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F87" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G87" s="26" t="s">
-        <v>196</v>
+        <v>35</v>
       </c>
       <c r="H87" s="27">
         <f t="shared" si="0"/>
@@ -4373,25 +4377,25 @@
         <v>0.4548611111111111</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:10">
       <c r="A88" s="20">
         <v>46169</v>
       </c>
       <c r="B88" s="20" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C88" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D88" s="25"/>
       <c r="E88" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F88" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G88" s="26" t="s">
-        <v>191</v>
+        <v>30</v>
       </c>
       <c r="H88" s="27">
         <f t="shared" si="0"/>
@@ -4404,25 +4408,25 @@
         <v>0.47430555555555554</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:10">
       <c r="A89" s="20">
         <v>46169</v>
       </c>
       <c r="B89" s="20" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C89" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D89" s="25"/>
       <c r="E89" s="25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F89" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G89" s="26" t="s">
-        <v>196</v>
+        <v>35</v>
       </c>
       <c r="H89" s="27">
         <f t="shared" si="0"/>
@@ -4435,25 +4439,25 @@
         <v>0.53472222222222221</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:10">
       <c r="A90" s="20">
         <v>46169</v>
       </c>
       <c r="B90" s="20" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C90" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D90" s="25"/>
       <c r="E90" s="25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F90" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G90" s="26" t="s">
-        <v>196</v>
+        <v>35</v>
       </c>
       <c r="H90" s="27">
         <f t="shared" si="0"/>
@@ -4466,25 +4470,25 @@
         <v>0.60416666666666663</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:10">
       <c r="A91" s="20">
         <v>46169</v>
       </c>
       <c r="B91" s="20" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C91" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D91" s="25"/>
       <c r="E91" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F91" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G91" s="26" t="s">
-        <v>193</v>
+        <v>29</v>
       </c>
       <c r="H91" s="27">
         <f t="shared" si="0"/>
@@ -4497,25 +4501,25 @@
         <v>0.66319444444444442</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:10">
       <c r="A92" s="20">
         <v>46169</v>
       </c>
       <c r="B92" s="20" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C92" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D92" s="25"/>
       <c r="E92" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F92" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G92" s="26" t="s">
-        <v>197</v>
+        <v>36</v>
       </c>
       <c r="H92" s="27">
         <f t="shared" si="0"/>
@@ -4528,25 +4532,25 @@
         <v>0.75069444444444444</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:10">
       <c r="A93" s="20">
         <v>46170</v>
       </c>
       <c r="B93" s="20" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C93" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D93" s="25"/>
       <c r="E93" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F93" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G93" s="26" t="s">
-        <v>189</v>
+        <v>26</v>
       </c>
       <c r="H93" s="27">
         <f t="shared" si="0"/>
@@ -4559,25 +4563,25 @@
         <v>0.35625000000000001</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:10">
       <c r="A94" s="20">
         <v>46170</v>
       </c>
       <c r="B94" s="20" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C94" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D94" s="25"/>
       <c r="E94" s="25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F94" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G94" s="26" t="s">
-        <v>196</v>
+        <v>35</v>
       </c>
       <c r="H94" s="27">
         <f t="shared" si="0"/>
@@ -4590,25 +4594,25 @@
         <v>0.39583333333333331</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:10">
       <c r="A95" s="20">
         <v>46170</v>
       </c>
       <c r="B95" s="20" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C95" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D95" s="25"/>
       <c r="E95" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F95" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G95" s="26" t="s">
-        <v>193</v>
+        <v>29</v>
       </c>
       <c r="H95" s="27">
         <f t="shared" si="0"/>
@@ -4621,25 +4625,25 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:10">
       <c r="A96" s="20">
         <v>46170</v>
       </c>
       <c r="B96" s="20" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C96" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D96" s="25"/>
       <c r="E96" s="25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F96" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G96" s="26" t="s">
-        <v>196</v>
+        <v>35</v>
       </c>
       <c r="H96" s="27">
         <f t="shared" si="0"/>
@@ -4652,25 +4656,25 @@
         <v>0.4548611111111111</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:10">
       <c r="A97" s="20">
         <v>46170</v>
       </c>
       <c r="B97" s="20" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C97" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D97" s="25"/>
       <c r="E97" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F97" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G97" s="26" t="s">
-        <v>191</v>
+        <v>30</v>
       </c>
       <c r="H97" s="27">
         <f t="shared" si="0"/>
@@ -4683,25 +4687,25 @@
         <v>0.48541666666666666</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:10">
       <c r="A98" s="20">
         <v>46170</v>
       </c>
       <c r="B98" s="20" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C98" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D98" s="25"/>
       <c r="E98" s="25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F98" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G98" s="26" t="s">
-        <v>196</v>
+        <v>35</v>
       </c>
       <c r="H98" s="27">
         <f t="shared" si="0"/>
@@ -4714,25 +4718,25 @@
         <v>0.57986111111111116</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:10">
       <c r="A99" s="20">
         <v>46170</v>
       </c>
       <c r="B99" s="20" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C99" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D99" s="25"/>
       <c r="E99" s="25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F99" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G99" s="26" t="s">
-        <v>196</v>
+        <v>35</v>
       </c>
       <c r="H99" s="27">
         <f t="shared" si="0"/>
@@ -4745,25 +4749,25 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:10">
       <c r="A100" s="20">
         <v>46170</v>
       </c>
       <c r="B100" s="20" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C100" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D100" s="25"/>
       <c r="E100" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F100" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G100" s="26" t="s">
-        <v>193</v>
+        <v>29</v>
       </c>
       <c r="H100" s="27">
         <f t="shared" si="0"/>
@@ -4776,25 +4780,25 @@
         <v>0.66319444444444442</v>
       </c>
     </row>
-    <row r="101" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:10" ht="25.15">
       <c r="A101" s="20">
         <v>46170</v>
       </c>
       <c r="B101" s="20" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C101" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D101" s="25"/>
       <c r="E101" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F101" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G101" s="26" t="s">
-        <v>190</v>
+        <v>31</v>
       </c>
       <c r="H101" s="27">
         <f t="shared" si="0"/>
@@ -4807,25 +4811,25 @@
         <v>0.70486111111111116</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:10">
       <c r="A102" s="20">
         <v>46170</v>
       </c>
       <c r="B102" s="20" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C102" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D102" s="25"/>
       <c r="E102" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F102" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G102" s="26" t="s">
-        <v>197</v>
+        <v>36</v>
       </c>
       <c r="H102" s="27">
         <f t="shared" si="0"/>
@@ -4838,25 +4842,25 @@
         <v>0.7270833333333333</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:10">
       <c r="A103" s="20">
         <v>46171</v>
       </c>
       <c r="B103" s="20" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C103" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D103" s="25"/>
       <c r="E103" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F103" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G103" s="26" t="s">
-        <v>189</v>
+        <v>26</v>
       </c>
       <c r="H103" s="27">
         <f t="shared" si="0"/>
@@ -4869,25 +4873,25 @@
         <v>0.33611111111111114</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:10">
       <c r="A104" s="20">
         <v>46171</v>
       </c>
       <c r="B104" s="20" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C104" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D104" s="25"/>
       <c r="E104" s="25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F104" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G104" s="26" t="s">
-        <v>196</v>
+        <v>35</v>
       </c>
       <c r="H104" s="27">
         <f t="shared" si="0"/>
@@ -4900,25 +4904,25 @@
         <v>0.4548611111111111</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:10">
       <c r="A105" s="20">
         <v>46171</v>
       </c>
       <c r="B105" s="20" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C105" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D105" s="25"/>
       <c r="E105" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F105" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G105" s="26" t="s">
-        <v>191</v>
+        <v>30</v>
       </c>
       <c r="H105" s="27">
         <f t="shared" si="0"/>
@@ -4931,25 +4935,25 @@
         <v>0.47986111111111113</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:10">
       <c r="A106" s="20">
         <v>46171</v>
       </c>
       <c r="B106" s="20" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C106" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D106" s="25"/>
       <c r="E106" s="25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F106" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G106" s="26" t="s">
-        <v>196</v>
+        <v>35</v>
       </c>
       <c r="H106" s="27">
         <f t="shared" si="0"/>
@@ -4962,25 +4966,25 @@
         <v>0.53819444444444442</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:10">
       <c r="A107" s="20">
         <v>46171</v>
       </c>
       <c r="B107" s="20" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C107" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D107" s="25"/>
       <c r="E107" s="25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="F107" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G107" s="26" t="s">
-        <v>196</v>
+        <v>35</v>
       </c>
       <c r="H107" s="27">
         <f t="shared" si="0"/>
@@ -4993,25 +4997,25 @@
         <v>0.66319444444444442</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:10" ht="25.15">
       <c r="A108" s="20">
         <v>46171</v>
       </c>
       <c r="B108" s="20" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C108" s="25" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D108" s="25"/>
       <c r="E108" s="25" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F108" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G108" s="26" t="s">
-        <v>190</v>
+        <v>31</v>
       </c>
       <c r="H108" s="27">
         <f t="shared" si="0"/>
@@ -5024,12 +5028,12 @@
         <v>0.7319444444444444</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:10">
       <c r="A109" s="29">
         <v>46172</v>
       </c>
       <c r="B109" s="29" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C109" s="30"/>
       <c r="D109" s="30"/>
@@ -5043,12 +5047,12 @@
       <c r="I109" s="33"/>
       <c r="J109" s="33"/>
     </row>
-    <row r="110" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" ht="13.15">
       <c r="A110" s="29">
         <v>46173</v>
       </c>
       <c r="B110" s="29" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C110" s="30"/>
       <c r="D110" s="69"/>
@@ -5062,7 +5066,7 @@
       <c r="I110" s="70"/>
       <c r="J110" s="30"/>
     </row>
-    <row r="111" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
       <c r="A111" s="44"/>
       <c r="B111" s="43"/>
       <c r="C111" s="43"/>
@@ -5073,35 +5077,35 @@
       <c r="H111" s="34"/>
       <c r="I111" s="35"/>
     </row>
-    <row r="112" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" ht="13.9" customHeight="1">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="3"/>
       <c r="D112" s="4"/>
       <c r="E112" s="5" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="F112" s="6">
         <v>160</v>
       </c>
       <c r="H112" s="38"/>
     </row>
-    <row r="113" spans="1:8" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" ht="13.9" customHeight="1" thickBot="1">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="7"/>
       <c r="D113" s="1"/>
       <c r="E113" s="8" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="F113" s="9">
         <v>20</v>
       </c>
       <c r="H113" s="38"/>
     </row>
-    <row r="114" spans="1:8" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" ht="13.9" customHeight="1" thickBot="1">
       <c r="A114" s="93" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="B114" s="93"/>
       <c r="C114" s="93"/>
@@ -5110,13 +5114,13 @@
       <c r="F114" s="1"/>
       <c r="H114" s="38"/>
     </row>
-    <row r="115" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" ht="13.9" customHeight="1">
       <c r="A115" s="11"/>
       <c r="B115" s="11"/>
       <c r="C115" s="4"/>
       <c r="D115" s="4"/>
       <c r="E115" s="12" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F115" s="13">
         <f>SUMIF(F9:F110,"Billable",H9:H110)</f>
@@ -5124,37 +5128,37 @@
       </c>
       <c r="H115" s="36"/>
     </row>
-    <row r="116" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8" ht="14.45" thickBot="1">
       <c r="A116" s="94" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="B116" s="94"/>
       <c r="C116" s="94"/>
       <c r="D116" s="14"/>
       <c r="E116" s="15" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F116" s="16">
         <f>SUMIF(F9:F110,"Non-Billable",H9:H110)</f>
-        <v>6.8652777777777771</v>
+        <v>6.9784722222222211</v>
       </c>
       <c r="H116" s="38"/>
     </row>
-    <row r="117" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" ht="15" customHeight="1" thickBot="1">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
       <c r="D117" s="1"/>
       <c r="E117" s="17" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F117" s="42">
         <f>F115+F116</f>
-        <v>6.8652777777777771</v>
+        <v>6.9784722222222211</v>
       </c>
       <c r="H117" s="38"/>
     </row>
-    <row r="118" spans="1:8" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" ht="13.9" thickBot="1">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -5163,18 +5167,18 @@
       <c r="F118" s="1"/>
       <c r="H118" s="38"/>
     </row>
-    <row r="119" spans="1:8" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" ht="13.9" thickBot="1">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
       <c r="D119" s="1"/>
       <c r="E119" s="18" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="F119" s="19"/>
       <c r="H119" s="38"/>
     </row>
-    <row r="120" spans="1:8" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" ht="13.15" thickBot="1">
       <c r="E120" s="37"/>
       <c r="H120" s="38"/>
     </row>
@@ -5185,56 +5189,56 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A6:B6 D6:E7">
-    <cfRule type="containsText" dxfId="15" priority="21" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="22" priority="21" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="22" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="21" priority="22" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="23" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="20" priority="23" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="24" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="19" priority="24" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="25" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="18" priority="25" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="26" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="17" priority="26" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="27" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B120">
-    <cfRule type="containsText" dxfId="8" priority="8" operator="containsText" text="Saturday">
+    <cfRule type="containsText" dxfId="15" priority="8" operator="containsText" text="Saturday">
       <formula>NOT(ISERROR(SEARCH("Saturday",B7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="9" operator="containsText" text="Sunday">
+    <cfRule type="containsText" dxfId="14" priority="9" operator="containsText" text="Sunday">
       <formula>NOT(ISERROR(SEARCH("Sunday",B7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D110:E112 D114:E116 E119">
-    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",D110)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="12" priority="2" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",D110)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="11" priority="3" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",D110)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="10" priority="4" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",D110)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="9" priority="5" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",D110)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="6" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="8" priority="6" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",D110)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5289,735 +5293,735 @@
     <tabColor theme="4"/>
   </sheetPr>
   <dimension ref="B2:J76"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="8.69921875" style="50"/>
+    <col min="1" max="1" width="8.75" style="50"/>
     <col min="2" max="2" width="25.5" style="50" customWidth="1"/>
-    <col min="3" max="3" width="8.69921875" style="50"/>
-    <col min="4" max="4" width="19.296875" style="50" customWidth="1"/>
-    <col min="5" max="5" width="8.69921875" style="50"/>
-    <col min="6" max="6" width="21.796875" style="50" customWidth="1"/>
-    <col min="7" max="16384" width="8.69921875" style="50"/>
+    <col min="3" max="3" width="8.75" style="50"/>
+    <col min="4" max="4" width="19.25" style="50" customWidth="1"/>
+    <col min="5" max="5" width="8.75" style="50"/>
+    <col min="6" max="6" width="21.75" style="50" customWidth="1"/>
+    <col min="7" max="16384" width="8.75" style="50"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:10" ht="15" thickBot="1">
       <c r="B2" s="62" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D2" s="51" t="s">
-        <v>101</v>
+        <v>45</v>
       </c>
       <c r="F2" s="50" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H2" s="50" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="J2" s="51" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10">
       <c r="B3" s="62" t="s">
-        <v>102</v>
+        <v>48</v>
       </c>
       <c r="D3" s="67" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="F3" s="53" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="H3" s="64" t="s">
-        <v>99</v>
+        <v>51</v>
       </c>
       <c r="I3" s="71"/>
       <c r="J3" s="54" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10">
       <c r="B4" s="62" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
       <c r="D4" s="52" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="F4" s="55" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="H4" s="73" t="s">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="I4" s="64"/>
       <c r="J4" s="56" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10">
       <c r="B5" s="62" t="s">
-        <v>114</v>
+        <v>56</v>
       </c>
       <c r="D5" s="67" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="F5" s="57" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="H5" s="64" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="I5" s="72"/>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:10">
       <c r="B6" s="62" t="s">
-        <v>185</v>
+        <v>60</v>
       </c>
       <c r="D6" s="52" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="F6" s="55" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="H6" s="71" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="I6" s="73"/>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:10">
       <c r="B7" s="62" t="s">
-        <v>103</v>
+        <v>64</v>
       </c>
       <c r="D7" s="67" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="F7" s="57" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="H7" s="63" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="I7" s="74"/>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:10">
       <c r="B8" s="62" t="s">
-        <v>186</v>
+        <v>68</v>
       </c>
       <c r="D8" s="52" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="F8" s="55" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="H8" s="74" t="s">
-        <v>117</v>
+        <v>71</v>
       </c>
       <c r="I8" s="71"/>
       <c r="J8" s="50" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10">
       <c r="B9" s="62" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="D9" s="67" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="F9" s="57" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="H9" s="75" t="s">
-        <v>153</v>
+        <v>76</v>
       </c>
       <c r="I9" s="71"/>
       <c r="J9" s="50" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10">
       <c r="B10" s="62" t="s">
-        <v>184</v>
+        <v>78</v>
       </c>
       <c r="D10" s="52" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="F10" s="55" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="H10" s="79" t="s">
-        <v>172</v>
+        <v>1</v>
       </c>
       <c r="I10" s="74"/>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10">
       <c r="B11" s="62" t="s">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="D11" s="67" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="F11" s="57" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="H11" s="75" t="s">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="I11" s="74"/>
       <c r="J11" s="50" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10">
       <c r="B12" s="62" t="s">
-        <v>122</v>
+        <v>86</v>
       </c>
       <c r="F12" s="55" t="s">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="H12" s="79" t="s">
-        <v>173</v>
+        <v>88</v>
       </c>
       <c r="I12" s="75"/>
       <c r="J12" s="50" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10">
       <c r="B13" s="62" t="s">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="F13" s="57" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="H13" s="76" t="s">
-        <v>120</v>
+        <v>92</v>
       </c>
       <c r="I13" s="75"/>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:10">
       <c r="B14" s="62" t="s">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="D14" s="58"/>
       <c r="F14" s="55" t="s">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="H14" s="77" t="s">
-        <v>123</v>
+        <v>95</v>
       </c>
       <c r="I14" s="76"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:10">
       <c r="B15" s="62" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="D15" s="59"/>
       <c r="F15" s="57" t="s">
-        <v>56</v>
+        <v>97</v>
       </c>
       <c r="H15" s="75" t="s">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="I15" s="75"/>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:10">
       <c r="B16" s="62" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D16" s="59"/>
       <c r="F16" s="55" t="s">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="H16" s="76" t="s">
-        <v>170</v>
+        <v>101</v>
       </c>
       <c r="I16" s="77"/>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9">
       <c r="B17" s="62" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="D17" s="59"/>
       <c r="F17" s="57" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="H17" s="63" t="s">
-        <v>61</v>
+        <v>104</v>
       </c>
       <c r="I17" s="75"/>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:9">
       <c r="B18" s="62" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D18" s="59"/>
       <c r="F18" s="55" t="s">
-        <v>60</v>
+        <v>106</v>
       </c>
       <c r="H18" s="80" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="I18" s="77"/>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:9">
       <c r="B19" s="62" t="s">
-        <v>180</v>
+        <v>108</v>
       </c>
       <c r="D19" s="59"/>
       <c r="F19" s="57" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="H19" s="66" t="s">
-        <v>166</v>
+        <v>109</v>
       </c>
       <c r="I19" s="78"/>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:9">
       <c r="B20" s="62" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="D20" s="59"/>
       <c r="F20" s="55" t="s">
-        <v>63</v>
+        <v>111</v>
       </c>
       <c r="H20" s="66" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="I20" s="76"/>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:9">
       <c r="B21" s="62" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="D21" s="59"/>
       <c r="F21" s="57" t="s">
-        <v>64</v>
+        <v>114</v>
       </c>
       <c r="H21" s="84" t="s">
-        <v>74</v>
+        <v>115</v>
       </c>
       <c r="I21" s="74"/>
     </row>
-    <row r="22" spans="2:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:9" ht="27.6">
       <c r="B22" s="62" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="D22" s="59"/>
       <c r="F22" s="55" t="s">
-        <v>66</v>
+        <v>117</v>
       </c>
       <c r="H22" s="89" t="s">
-        <v>155</v>
+        <v>118</v>
       </c>
       <c r="I22" s="79"/>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:9">
       <c r="B23" s="62" t="s">
-        <v>183</v>
+        <v>119</v>
       </c>
       <c r="D23" s="59"/>
       <c r="F23" s="57" t="s">
-        <v>68</v>
+        <v>120</v>
       </c>
       <c r="H23" s="82" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="I23" s="80"/>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:9">
       <c r="B24" s="62" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="D24" s="59"/>
       <c r="F24" s="55" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="H24" s="66" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="I24" s="81"/>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:9">
       <c r="B25" s="62" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D25" s="59"/>
       <c r="F25" s="57" t="s">
-        <v>70</v>
+        <v>125</v>
       </c>
       <c r="H25" s="84" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="I25" s="82"/>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:9">
       <c r="B26" s="62" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="F26" s="55" t="s">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="H26" s="66" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9">
       <c r="B27" s="62" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D27" s="59"/>
       <c r="F27" s="57" t="s">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="H27" s="81" t="s">
-        <v>174</v>
+        <v>132</v>
       </c>
       <c r="I27" s="80"/>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:9">
       <c r="B28" s="62" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D28" s="59"/>
       <c r="F28" s="55" t="s">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="H28" s="84" t="s">
-        <v>167</v>
+        <v>135</v>
       </c>
       <c r="I28" s="66"/>
     </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:9">
       <c r="B29" s="62" t="s">
-        <v>165</v>
+        <v>136</v>
       </c>
       <c r="F29" s="57" t="s">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="H29" s="82" t="s">
-        <v>42</v>
+        <v>138</v>
       </c>
       <c r="I29" s="83"/>
     </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:9">
       <c r="B30" s="62" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F30" s="55" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="H30" s="65" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="I30" s="81"/>
     </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:9">
       <c r="B31" s="62" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="F31" s="57" t="s">
-        <v>79</v>
+        <v>143</v>
       </c>
       <c r="H31" s="65" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9">
+      <c r="B32" s="62" t="s">
+        <v>145</v>
+      </c>
+      <c r="F32" s="55" t="s">
+        <v>146</v>
+      </c>
+      <c r="H32" s="83" t="s">
+        <v>147</v>
+      </c>
+      <c r="I32" s="82"/>
+    </row>
+    <row r="33" spans="2:9">
+      <c r="B33" s="62" t="s">
+        <v>148</v>
+      </c>
+      <c r="F33" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="H33" s="90" t="s">
+        <v>149</v>
+      </c>
+      <c r="I33" s="82"/>
+    </row>
+    <row r="34" spans="2:9">
+      <c r="B34" s="62" t="s">
+        <v>150</v>
+      </c>
+      <c r="F34" s="55" t="s">
+        <v>151</v>
+      </c>
+      <c r="H34" s="81" t="s">
+        <v>152</v>
+      </c>
+      <c r="I34" s="65"/>
+    </row>
+    <row r="35" spans="2:9">
+      <c r="B35" s="62" t="s">
+        <v>153</v>
+      </c>
+      <c r="F35" s="57" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B32" s="62" t="s">
-        <v>78</v>
-      </c>
-      <c r="F32" s="55" t="s">
-        <v>80</v>
-      </c>
-      <c r="H32" s="83" t="s">
+      <c r="H35" s="86" t="s">
+        <v>155</v>
+      </c>
+      <c r="I35" s="81"/>
+    </row>
+    <row r="36" spans="2:9">
+      <c r="B36" s="62" t="s">
         <v>156</v>
       </c>
-      <c r="I32" s="82"/>
-    </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B33" s="62" t="s">
-        <v>137</v>
-      </c>
-      <c r="F33" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="H33" s="90" t="s">
-        <v>65</v>
-      </c>
-      <c r="I33" s="82"/>
-    </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B34" s="62" t="s">
-        <v>83</v>
-      </c>
-      <c r="F34" s="55" t="s">
-        <v>84</v>
-      </c>
-      <c r="H34" s="81" t="s">
-        <v>175</v>
-      </c>
-      <c r="I34" s="65"/>
-    </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B35" s="62" t="s">
-        <v>138</v>
-      </c>
-      <c r="F35" s="57" t="s">
-        <v>85</v>
-      </c>
-      <c r="H35" s="86" t="s">
+      <c r="F36" s="55" t="s">
         <v>157</v>
-      </c>
-      <c r="I35" s="81"/>
-    </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B36" s="62" t="s">
-        <v>182</v>
-      </c>
-      <c r="F36" s="55" t="s">
-        <v>87</v>
       </c>
       <c r="H36" s="83" t="s">
         <v>158</v>
       </c>
       <c r="I36" s="74"/>
     </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:9">
       <c r="B37" s="62" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="F37" s="55" t="s">
-        <v>88</v>
+        <v>160</v>
       </c>
       <c r="H37" s="84" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="I37" s="82"/>
     </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:9">
       <c r="B38" s="62" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="F38" s="55" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="H38" s="81" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="I38" s="81"/>
     </row>
-    <row r="39" spans="2:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:9" ht="27.6">
       <c r="B39" s="62" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="F39" s="55" t="s">
-        <v>91</v>
+        <v>165</v>
       </c>
       <c r="H39" s="81" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="I39" s="83"/>
     </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:9">
       <c r="B40" s="62" t="s">
-        <v>90</v>
+        <v>167</v>
       </c>
       <c r="F40" s="57" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="H40" s="65" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="I40" s="84"/>
     </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:9">
       <c r="B41" s="62" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D41" s="61"/>
       <c r="H41" s="83" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="I41" s="84"/>
     </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:9">
       <c r="B42" s="62" t="s">
-        <v>97</v>
+        <v>172</v>
       </c>
       <c r="H42" s="84" t="s">
-        <v>139</v>
+        <v>173</v>
       </c>
       <c r="I42" s="81"/>
     </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:9">
       <c r="B43" s="62" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="H43" s="81" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="I43" s="83"/>
     </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:9">
       <c r="B44" s="92" t="s">
-        <v>146</v>
+        <v>176</v>
       </c>
       <c r="H44" s="83" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.3">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9">
       <c r="H45" s="84" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="I45" s="82"/>
     </row>
-    <row r="46" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:9">
       <c r="H46" s="66" t="s">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="I46" s="85"/>
     </row>
-    <row r="47" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:9">
       <c r="B47" s="60"/>
       <c r="H47" s="84" t="s">
-        <v>37</v>
+        <v>180</v>
       </c>
       <c r="I47" s="84"/>
     </row>
-    <row r="48" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:9">
       <c r="H48" s="66" t="s">
-        <v>144</v>
+        <v>181</v>
       </c>
       <c r="I48" s="84"/>
     </row>
-    <row r="49" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="8:9">
       <c r="H49" s="81" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="I49" s="84"/>
     </row>
-    <row r="50" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="8:9">
       <c r="H50" s="66" t="s">
-        <v>55</v>
+        <v>183</v>
       </c>
       <c r="I50" s="84"/>
     </row>
-    <row r="51" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="8:9">
       <c r="H51" s="65" t="s">
-        <v>67</v>
+        <v>184</v>
       </c>
       <c r="I51" s="84"/>
     </row>
-    <row r="52" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="8:9">
       <c r="H52" s="84" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="53" spans="8:9" x14ac:dyDescent="0.3">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="53" spans="8:9">
       <c r="H53" s="81" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="I53" s="84"/>
     </row>
-    <row r="54" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="8:9">
       <c r="H54" s="65" t="s">
-        <v>86</v>
+        <v>187</v>
       </c>
       <c r="I54" s="83"/>
     </row>
-    <row r="55" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="8:9">
       <c r="H55" s="66" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="I55" s="83"/>
     </row>
-    <row r="56" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="8:9">
       <c r="H56" s="81" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="I56" s="66"/>
     </row>
-    <row r="57" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="8:9">
       <c r="H57" s="66" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
       <c r="I57" s="84"/>
     </row>
-    <row r="58" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="8:9">
       <c r="H58" s="66" t="s">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="I58" s="84"/>
     </row>
-    <row r="59" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="8:9">
       <c r="H59" s="84" t="s">
-        <v>148</v>
+        <v>192</v>
       </c>
       <c r="I59" s="87"/>
     </row>
-    <row r="60" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="8:9">
       <c r="H60" s="87" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
       <c r="I60" s="65"/>
     </row>
-    <row r="61" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="8:9">
       <c r="H61" s="65" t="s">
-        <v>109</v>
+        <v>194</v>
       </c>
       <c r="I61" s="82"/>
     </row>
-    <row r="62" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="8:9">
       <c r="H62" s="65" t="s">
-        <v>149</v>
+        <v>195</v>
       </c>
       <c r="I62" s="65"/>
     </row>
-    <row r="63" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="8:9">
       <c r="H63" s="82" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="64" spans="8:9" x14ac:dyDescent="0.3">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="64" spans="8:9">
       <c r="H64" s="91" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="65" spans="8:8" x14ac:dyDescent="0.3">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="65" spans="8:8">
       <c r="H65" s="83"/>
     </row>
-    <row r="66" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="8:8">
       <c r="H66" s="81"/>
     </row>
-    <row r="67" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="8:8">
       <c r="H67" s="84"/>
     </row>
-    <row r="68" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="8:8">
       <c r="H68" s="74"/>
     </row>
-    <row r="69" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="8:8">
       <c r="H69" s="84"/>
     </row>
-    <row r="70" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="8:8">
       <c r="H70" s="66"/>
     </row>
-    <row r="71" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="8:8">
       <c r="H71" s="81"/>
     </row>
-    <row r="72" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="8:8">
       <c r="H72" s="83"/>
     </row>
-    <row r="73" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="8:8">
       <c r="H73" s="72"/>
     </row>
-    <row r="74" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="8:8">
       <c r="H74" s="79"/>
     </row>
-    <row r="75" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="8:8">
       <c r="H75" s="88"/>
     </row>
-    <row r="76" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="8:8">
       <c r="H76" s="88"/>
     </row>
   </sheetData>
@@ -6042,15 +6046,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AD10A028B4ACBB47B37340D8D4079B36" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="436e80374471046821afb96e56969fce">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="819cb4b524acab89028d2f2d821df341" ns2:_="">
     <xsd:import namespace="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2"/>
@@ -6188,39 +6183,25 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A01E2E1-AD2B-4877-8D28-137FCC3DC11F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A01E2E1-AD2B-4877-8D28-137FCC3DC11F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE7E12A6-F517-46CD-BC2F-35B9AE2F3050}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD238E5F-22EC-4E92-9786-777D67AA4D84}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD238E5F-22EC-4E92-9786-777D67AA4D84}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE7E12A6-F517-46CD-BC2F-35B9AE2F3050}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
